--- a/etf_holdings/2026-09-17_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-17_common_daily_changes_summary.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,89 +464,89 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00991A(10,391,000)、00403A(3,000,000)、00993A(50,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-1,399,000)、00993A(-8,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>南亞塑膠</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>00991A(新納入)、00400A(1,180,000)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00991A(-1,399,000)、00993A(-8,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>00991A(10,391,000)、00993A(50,000)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00981A(-158,000)、00991A(-350,000)、00982A(-35,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>南亞塑膠</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00400A(1,180,000)</t>
+          <t>00981A(1,600,000)、00993A(10,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,17 +584,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00981A(1,600,000)、00993A(10,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-158,000)、00991A(-350,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-09-17_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-09-17_common_daily_changes_summary.xlsx
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,89 +464,89 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>00991A(10,391,000)、00403A(3,000,000)、00993A(50,000)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00991A(-1,399,000)、00993A(-8,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>南亞塑膠</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00400A(1,180,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-1,399,000)、00993A(-8,000)、00400A(全數賣出)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00991A(10,391,000)、00993A(50,000)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-158,000)、00991A(-350,000)、00982A(-35,000)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>南亞塑膠</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00981A(1,600,000)、00993A(10,000)</t>
+          <t>00991A(新納入)、00400A(1,180,000)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,12 +571,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -584,17 +584,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>全部減碼</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>00981A(1,600,000)、00993A(10,000)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00981A(-158,000)、00991A(-350,000)</t>
         </is>
       </c>
     </row>
